--- a/src/test/resources/Developer_testing.xlsx
+++ b/src/test/resources/Developer_testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2521759_cognizant_com/Documents/Desktop/synergia-automation/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="8_{2729FC6E-3E59-4291-94CF-9383BE038F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E550BCE-5191-424E-BFDF-853D044F2EAD}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{2729FC6E-3E59-4291-94CF-9383BE038F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F487C10-DBC5-4330-A255-006B4EC1E3D2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9C82953E-F790-4222-B175-F96F9F716250}"/>
   </bookViews>
